--- a/data/trans_dic/IP16B01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios</t>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,83; 100,0</t>
+          <t>85,83; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,04; 100,0</t>
+          <t>75,34; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,97; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,46; 100,0</t>
+          <t>79,98; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,7; 100,0</t>
+          <t>92,94; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83,68; 98,22</t>
+          <t>84,37; 98,23</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,74</t>
+          <t>0,0; 9,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,89; 90,88</t>
+          <t>70,0; 90,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,94; 91,51</t>
+          <t>68,91; 91,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>79,6; 95,81</t>
+          <t>81,09; 96,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,01; 97,46</t>
+          <t>74,85; 97,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,82; 92,28</t>
+          <t>80,06; 92,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76,42; 92,23</t>
+          <t>77,64; 92,7</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,76; 87,95</t>
+          <t>44,5; 87,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 93,82</t>
+          <t>66,42; 94,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>76,2; 100,0</t>
+          <t>80,05; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,23; 84,65</t>
+          <t>40,34; 87,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,25; 91,36</t>
+          <t>64,56; 91,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,45; 88,39</t>
+          <t>63,89; 87,7</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,23; 88,9</t>
+          <t>55,81; 89,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,3; 80,29</t>
+          <t>30,17; 82,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,57; 100,0</t>
+          <t>56,3; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,17; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,68; 88,42</t>
+          <t>65,0; 88,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,0; 92,67</t>
+          <t>63,55; 92,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,19; 88,06</t>
+          <t>75,35; 88,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,73; 88,63</t>
+          <t>73,88; 87,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,87; 96,99</t>
+          <t>88,05; 97,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,16; 93,98</t>
+          <t>80,09; 93,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,68; 91,27</t>
+          <t>83,55; 91,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80,18; 89,58</t>
+          <t>79,58; 89,15</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos recetados por el médico para el catarro, gripe, garganta, bronquios (tasa de respuesta: 99,34%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15041</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>26654</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16016</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>52313</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>31058</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23098; 26913</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12312; 16342</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13401; 16756</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>49785; 53567</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>27927; 32512</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22845</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>44461</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23349</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>74918</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>46194</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4114</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26034; 33777</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19043; 25407</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39725; 47122</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19494; 25390</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4393</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>68995; 79295</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>41676; 49761</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19327</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13174</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8594</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>23515</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27920</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6603; 12981</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15332; 21740</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11004; 13746</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5228; 11278</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18453; 26256</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23027; 31612</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14416</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8165</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11021</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>22580</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16226</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10749; 17152</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2816; 7655</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5382; 9560</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>18734; 25464</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12937; 18818</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80874</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62418</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92453</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>58981</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>173326</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>121399</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4707</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73996; 86422</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>56439; 67099</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>87123; 96011</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>53488; 62610</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5026</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>164724; 179957</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>113939; 127644</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16B01-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16B01-Edad-trans_dic.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,83; 100,0</t>
+          <t>83,56; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,34; 100,0</t>
+          <t>71,79; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,98; 100,0</t>
+          <t>76,62; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,94; 100,0</t>
+          <t>92,74; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,37; 98,23</t>
+          <t>83,36; 98,25</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,52</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,0; 90,81</t>
+          <t>70,84; 90,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68,91; 91,94</t>
+          <t>67,6; 92,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,09; 96,19</t>
+          <t>81,55; 96,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,85; 97,49</t>
+          <t>76,51; 97,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>80,06; 92,01</t>
+          <t>79,95; 92,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,64; 92,7</t>
+          <t>76,61; 92,14</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,5; 87,48</t>
+          <t>45,26; 86,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,42; 94,18</t>
+          <t>66,67; 93,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80,05; 100,0</t>
+          <t>77,76; 100,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,34; 87,02</t>
+          <t>42,23; 85,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>64,56; 91,85</t>
+          <t>67,91; 93,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63,89; 87,7</t>
+          <t>63,04; 87,62</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,81; 89,05</t>
+          <t>55,73; 89,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 82,01</t>
+          <t>26,86; 79,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,3; 100,0</t>
+          <t>58,73; 100,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,0; 88,35</t>
+          <t>61,92; 88,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63,55; 92,45</t>
+          <t>61,54; 91,36</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>75,35; 88,0</t>
+          <t>75,02; 87,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,88; 87,83</t>
+          <t>73,09; 87,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,05; 97,03</t>
+          <t>87,96; 96,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,09; 93,75</t>
+          <t>80,18; 93,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,55; 91,28</t>
+          <t>83,82; 91,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>79,58; 89,15</t>
+          <t>79,46; 89,31</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>23098; 26913</t>
+          <t>22488; 26913</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12312; 16342</t>
+          <t>11732; 16342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13401; 16756</t>
+          <t>12839; 16756</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49785; 53567</t>
+          <t>49679; 53567</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27927; 32512</t>
+          <t>27593; 32520</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4114</t>
+          <t>0; 4081</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26034; 33777</t>
+          <t>26346; 33788</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19043; 25407</t>
+          <t>18682; 25429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1600,27 +1600,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39725; 47122</t>
+          <t>39948; 47106</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19494; 25390</t>
+          <t>19928; 25399</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4393</t>
+          <t>0; 4873</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68995; 79295</t>
+          <t>68899; 79312</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41676; 49761</t>
+          <t>41125; 49460</t>
         </is>
       </c>
     </row>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6603; 12981</t>
+          <t>6717; 12792</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15332; 21740</t>
+          <t>15390; 21691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11004; 13746</t>
+          <t>10689; 13746</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5228; 11278</t>
+          <t>5474; 11043</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18453; 26256</t>
+          <t>19413; 26646</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23027; 31612</t>
+          <t>22721; 31580</t>
         </is>
       </c>
     </row>
@@ -1911,12 +1911,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10749; 17152</t>
+          <t>10735; 17186</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2816; 7655</t>
+          <t>2507; 7427</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5382; 9560</t>
+          <t>5615; 9560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18734; 25464</t>
+          <t>17847; 25434</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12937; 18818</t>
+          <t>12527; 18596</t>
         </is>
       </c>
     </row>
@@ -2069,17 +2069,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 4725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73996; 86422</t>
+          <t>73677; 86225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56439; 67099</t>
+          <t>55837; 67045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2089,27 +2089,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>87123; 96011</t>
+          <t>87037; 95751</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53488; 62610</t>
+          <t>53546; 62516</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5026</t>
+          <t>0; 4704</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164724; 179957</t>
+          <t>165258; 180086</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>113939; 127644</t>
+          <t>113767; 127868</t>
         </is>
       </c>
     </row>
